--- a/Sindhi Muslim/Result Sheet/Class 2 - Students Result Sheet.xlsx
+++ b/Sindhi Muslim/Result Sheet/Class 2 - Students Result Sheet.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Result Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C6CC6D-439C-4478-9451-E99F87CCC7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0D00E1-D92F-49F4-8496-D57A0AA6B449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A3810461-FCAA-4427-95C3-213E25AAD5DA}"/>
   </bookViews>
   <sheets>
-    <sheet name="Class - 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Class - 2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Class - 1'!$1:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Class - 2'!$1:$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="118">
   <si>
     <t>GOVERNMENT HIGH SCHOOL SINDHI JAMAAT CO-OPERATIVE HOUSING SOCIETY</t>
   </si>
@@ -130,9 +130,6 @@
   </si>
   <si>
     <t>Drawing</t>
-  </si>
-  <si>
-    <t>Grade</t>
   </si>
   <si>
     <t>Two</t>
@@ -523,6 +520,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -531,12 +534,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -866,91 +863,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
     </row>
     <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="10" t="s">
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="P3" s="12" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="47.25" x14ac:dyDescent="0.2">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
       <c r="F4" s="6" t="s">
         <v>29</v>
       </c>
@@ -969,77 +966,63 @@
       <c r="K4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="7">
-        <v>100</v>
-      </c>
-      <c r="G5" s="7">
-        <v>100</v>
-      </c>
-      <c r="H5" s="7">
-        <v>100</v>
-      </c>
-      <c r="I5" s="7">
-        <v>100</v>
-      </c>
-      <c r="J5" s="7">
-        <v>100</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="7">
-        <v>500</v>
-      </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
     </row>
     <row r="6" spans="1:16" s="4" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
     </row>
     <row r="7" spans="1:16" s="4" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>1</v>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>34</v>
-      </c>
       <c r="E7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -1058,14 +1041,14 @@
         <v>2</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>36</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -1084,14 +1067,14 @@
         <v>3</v>
       </c>
       <c r="B9" s="2"/>
-      <c r="C9" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="12" t="s">
+      <c r="C9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -1110,14 +1093,14 @@
         <v>4</v>
       </c>
       <c r="B10" s="2"/>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>39</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -1136,14 +1119,14 @@
         <v>5</v>
       </c>
       <c r="B11" s="2"/>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>40</v>
+      <c r="D11" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -1162,14 +1145,14 @@
         <v>6</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>41</v>
+      <c r="D12" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -1188,14 +1171,14 @@
         <v>7</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="12" t="s">
+      <c r="C13" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -1214,14 +1197,14 @@
         <v>8</v>
       </c>
       <c r="B14" s="2"/>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>44</v>
-      </c>
       <c r="E14" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -1240,14 +1223,14 @@
         <v>9</v>
       </c>
       <c r="B15" s="2"/>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>46</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -1266,14 +1249,14 @@
         <v>10</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>48</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -1292,14 +1275,14 @@
         <v>11</v>
       </c>
       <c r="B17" s="2"/>
-      <c r="C17" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="12" t="s">
+      <c r="C17" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>23</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -1318,14 +1301,14 @@
         <v>12</v>
       </c>
       <c r="B18" s="2"/>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>51</v>
-      </c>
       <c r="E18" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -1344,14 +1327,14 @@
         <v>13</v>
       </c>
       <c r="B19" s="2"/>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="12" t="s">
-        <v>53</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -1370,14 +1353,14 @@
         <v>14</v>
       </c>
       <c r="B20" s="2"/>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>55</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -1396,14 +1379,14 @@
         <v>15</v>
       </c>
       <c r="B21" s="2"/>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D21" s="12" t="s">
-        <v>57</v>
-      </c>
       <c r="E21" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -1422,14 +1405,14 @@
         <v>16</v>
       </c>
       <c r="B22" s="2"/>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>59</v>
-      </c>
       <c r="E22" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -1448,14 +1431,14 @@
         <v>17</v>
       </c>
       <c r="B23" s="2"/>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>61</v>
-      </c>
       <c r="E23" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -1474,14 +1457,14 @@
         <v>18</v>
       </c>
       <c r="B24" s="2"/>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="12" t="s">
-        <v>63</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -1500,14 +1483,14 @@
         <v>19</v>
       </c>
       <c r="B25" s="2"/>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="12" t="s">
-        <v>65</v>
-      </c>
       <c r="E25" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -1526,14 +1509,14 @@
         <v>20</v>
       </c>
       <c r="B26" s="2"/>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="12" t="s">
-        <v>66</v>
+      <c r="D26" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -1552,14 +1535,14 @@
         <v>21</v>
       </c>
       <c r="B27" s="2"/>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="12" t="s">
-        <v>68</v>
-      </c>
       <c r="E27" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -1578,14 +1561,14 @@
         <v>22</v>
       </c>
       <c r="B28" s="2"/>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D28" s="12" t="s">
-        <v>70</v>
-      </c>
       <c r="E28" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -1604,14 +1587,14 @@
         <v>23</v>
       </c>
       <c r="B29" s="2"/>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D29" s="12" t="s">
-        <v>72</v>
-      </c>
       <c r="E29" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -1630,14 +1613,14 @@
         <v>24</v>
       </c>
       <c r="B30" s="2"/>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="12" t="s">
-        <v>72</v>
+      <c r="D30" s="9" t="s">
+        <v>71</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -1656,14 +1639,14 @@
         <v>25</v>
       </c>
       <c r="B31" s="2"/>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="12" t="s">
-        <v>74</v>
-      </c>
       <c r="E31" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -1682,14 +1665,14 @@
         <v>26</v>
       </c>
       <c r="B32" s="2"/>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D32" s="12" t="s">
-        <v>75</v>
+      <c r="D32" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -1704,38 +1687,38 @@
       <c r="P32" s="1"/>
     </row>
     <row r="33" spans="1:16" s="4" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
-      <c r="M33" s="13"/>
-      <c r="N33" s="13"/>
-      <c r="O33" s="13"/>
-      <c r="P33" s="13"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10"/>
     </row>
     <row r="34" spans="1:16" s="4" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>27</v>
       </c>
       <c r="B34" s="2"/>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D34" s="12" t="s">
-        <v>77</v>
-      </c>
       <c r="E34" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -1754,14 +1737,14 @@
         <v>28</v>
       </c>
       <c r="B35" s="2"/>
-      <c r="C35" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>59</v>
+      <c r="C35" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>58</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -1780,14 +1763,14 @@
         <v>29</v>
       </c>
       <c r="B36" s="2"/>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D36" s="12" t="s">
-        <v>79</v>
-      </c>
       <c r="E36" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -1806,14 +1789,14 @@
         <v>30</v>
       </c>
       <c r="B37" s="2"/>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D37" s="12" t="s">
-        <v>80</v>
+      <c r="D37" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -1832,14 +1815,14 @@
         <v>31</v>
       </c>
       <c r="B38" s="2"/>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D38" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D38" s="12" t="s">
-        <v>82</v>
-      </c>
       <c r="E38" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -1858,14 +1841,14 @@
         <v>32</v>
       </c>
       <c r="B39" s="2"/>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D39" s="12" t="s">
-        <v>84</v>
-      </c>
       <c r="E39" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -1884,14 +1867,14 @@
         <v>1</v>
       </c>
       <c r="B40" s="2"/>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="12" t="s">
-        <v>86</v>
-      </c>
       <c r="E40" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -1910,14 +1893,14 @@
         <v>2</v>
       </c>
       <c r="B41" s="2"/>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D41" s="12" t="s">
-        <v>88</v>
-      </c>
       <c r="E41" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -1936,14 +1919,14 @@
         <v>3</v>
       </c>
       <c r="B42" s="2"/>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="12" t="s">
-        <v>90</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -1962,14 +1945,14 @@
         <v>4</v>
       </c>
       <c r="B43" s="2"/>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D43" s="12" t="s">
-        <v>92</v>
-      </c>
       <c r="E43" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -1988,14 +1971,14 @@
         <v>5</v>
       </c>
       <c r="B44" s="2"/>
-      <c r="C44" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D44" s="12" t="s">
+      <c r="C44" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" s="9" t="s">
         <v>22</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -2014,14 +1997,14 @@
         <v>6</v>
       </c>
       <c r="B45" s="2"/>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -2040,14 +2023,14 @@
         <v>7</v>
       </c>
       <c r="B46" s="2"/>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D46" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="D46" s="12" t="s">
-        <v>95</v>
-      </c>
       <c r="E46" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -2066,14 +2049,14 @@
         <v>8</v>
       </c>
       <c r="B47" s="2"/>
-      <c r="C47" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D47" s="12" t="s">
+      <c r="C47" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D47" s="9" t="s">
         <v>16</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -2092,14 +2075,14 @@
         <v>9</v>
       </c>
       <c r="B48" s="2"/>
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D48" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D48" s="12" t="s">
-        <v>98</v>
-      </c>
       <c r="E48" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -2118,14 +2101,14 @@
         <v>10</v>
       </c>
       <c r="B49" s="8"/>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D49" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="D49" s="12" t="s">
-        <v>100</v>
-      </c>
       <c r="E49" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -2144,14 +2127,14 @@
         <v>11</v>
       </c>
       <c r="B50" s="2"/>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D50" s="12" t="s">
-        <v>102</v>
-      </c>
       <c r="E50" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -2170,14 +2153,14 @@
         <v>12</v>
       </c>
       <c r="B51" s="2"/>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D51" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="D51" s="12" t="s">
-        <v>104</v>
-      </c>
       <c r="E51" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -2196,14 +2179,14 @@
         <v>13</v>
       </c>
       <c r="B52" s="2"/>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D52" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D52" s="12" t="s">
-        <v>106</v>
-      </c>
       <c r="E52" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
@@ -2222,14 +2205,14 @@
         <v>14</v>
       </c>
       <c r="B53" s="2"/>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="D53" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="D53" s="12" t="s">
-        <v>108</v>
-      </c>
       <c r="E53" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -2248,14 +2231,14 @@
         <v>15</v>
       </c>
       <c r="B54" s="2"/>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D54" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="D54" s="12" t="s">
-        <v>110</v>
-      </c>
       <c r="E54" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -2274,14 +2257,14 @@
         <v>16</v>
       </c>
       <c r="B55" s="2"/>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D55" s="12" t="s">
-        <v>111</v>
+      <c r="D55" s="9" t="s">
+        <v>110</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -2300,14 +2283,14 @@
         <v>17</v>
       </c>
       <c r="B56" s="2"/>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D56" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D56" s="12" t="s">
-        <v>113</v>
-      </c>
       <c r="E56" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -2326,14 +2309,14 @@
         <v>18</v>
       </c>
       <c r="B57" s="2"/>
-      <c r="C57" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>108</v>
+      <c r="C57" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>107</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -2352,14 +2335,14 @@
         <v>19</v>
       </c>
       <c r="B58" s="2"/>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D58" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D58" s="12" t="s">
-        <v>116</v>
-      </c>
       <c r="E58" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -2378,14 +2361,14 @@
         <v>20</v>
       </c>
       <c r="B59" s="2"/>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D59" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="D59" s="12" t="s">
-        <v>118</v>
-      </c>
       <c r="E59" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
